--- a/Result/profitability/2706.xlsx
+++ b/Result/profitability/2706.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.15625</v>
+        <v>0.1475</v>
       </c>
       <c r="N2" t="n">
-        <v>77.86375</v>
+        <v>77.44999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.19125</v>
+        <v>0.215</v>
       </c>
       <c r="N3" t="n">
-        <v>77.45375</v>
+        <v>77.285</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.21</v>
+        <v>0.22125</v>
       </c>
       <c r="N4" t="n">
-        <v>76.35624999999999</v>
+        <v>76.0775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2475</v>
+        <v>0.24875</v>
       </c>
       <c r="N5" t="n">
-        <v>75.23125</v>
+        <v>75.05624999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24125</v>
+        <v>0.23875</v>
       </c>
       <c r="N6" t="n">
-        <v>74.1925</v>
+        <v>73.53999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>0.30125</v>
+        <v>0.315</v>
       </c>
       <c r="N7" t="n">
-        <v>72.41749999999999</v>
+        <v>72.05625000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.30625</v>
+        <v>0.315</v>
       </c>
       <c r="N8" t="n">
-        <v>70.78375</v>
+        <v>70.49250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.31625</v>
       </c>
       <c r="N9" t="n">
-        <v>69.57125000000001</v>
+        <v>69.57124999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0.30375</v>
       </c>
       <c r="N12" t="n">
-        <v>66.63375000000001</v>
+        <v>66.63374999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>88</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>66</v>
+      </c>
+      <c r="F75" t="n">
+        <v>75.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>66.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>76</v>
+      </c>
+      <c r="J75" t="n">
+        <v>135</v>
+      </c>
+      <c r="K75" t="n">
+        <v>107</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>77.51124999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4999999999999998</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.329999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03006451612903227</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.009999999999999981</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.399999999999991</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01828392320752237</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
